--- a/tests/mung/fixtures/sumprod_z1_2026-07-07.xlsx
+++ b/tests/mung/fixtures/sumprod_z1_2026-07-07.xlsx
@@ -1546,7 +1546,7 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1566,7 +1566,7 @@
         <v>0.25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
@@ -1626,7 +1626,7 @@
         <v>-1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -1646,7 +1646,7 @@
         <v>-1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
@@ -1793,12 +1793,12 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
@@ -1807,7 +1807,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1821,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1835,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1849,12 +1849,12 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -1863,12 +1863,12 @@
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1891,12 +1891,12 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -1905,7 +1905,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1919,12 +1919,12 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
@@ -1933,7 +1933,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
